--- a/assets/download/정산_기준표.xlsx
+++ b/assets/download/정산_기준표.xlsx
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="신청내역" displayName="신청내역" ref="A1:F1" headerRowCount="1">
-  <autoFilter ref="A1:F1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="신청내역" displayName="신청내역" ref="A1:F2" headerRowCount="1">
+  <autoFilter ref="A1:F2"/>
   <tableColumns count="6">
     <tableColumn id="1" name="신청번호"/>
     <tableColumn id="2" name="신청자"/>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -630,6 +630,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
